--- a/crates/xlstream-eval/tests/fixtures/aggregate/minifs_maxifs.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/aggregate/minifs_maxifs.xlsx
@@ -9,7 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="AggSource" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,12 +20,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="7">
-  <si>
-    <t xml:space="preserve">minifs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maxifs</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+  <si>
+    <t xml:space="preserve">region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minifs_1crit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxifs_1crit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minifs_2crit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxifs_2crit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minifs_nomatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxifs_nomatch</t>
   </si>
   <si>
     <t xml:space="preserve">EMEA</t>
@@ -314,7 +334,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -324,144 +344,376 @@
       <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <f aca="false">_xlfn.MINIFS(AggSource!B:B,AggSource!A:A,"EMEA",AggSource!C:C,"Sales")</f>
-        <v>500</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <f aca="false">_xlfn.MAXIFS(AggSource!B:B,AggSource!A:A,"EMEA",AggSource!C:C,"Sales")</f>
-        <v>600</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="0" t="n">
-        <v>500</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>300</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A2)</f>
+        <v>200</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A2)</f>
+        <v>600</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A2,B:B,B2)</f>
+        <v>500</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A2,B:B,B2)</f>
+        <v>600</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>700</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A3)</f>
+        <v>300</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A3)</f>
+        <v>800</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A3,B:B,B3)</f>
+        <v>300</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A3,B:B,B3)</f>
+        <v>300</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>13</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>700</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A4)</f>
+        <v>100</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A4)</f>
+        <v>700</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A4,B:B,B4)</f>
+        <v>450</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A4,B:B,B4)</f>
+        <v>700</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>400</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A5)</f>
+        <v>200</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A5)</f>
+        <v>600</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A5,B:B,B5)</f>
+        <v>200</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A5,B:B,B5)</f>
+        <v>350</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>600</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A6)</f>
+        <v>300</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A6)</f>
+        <v>800</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A6,B:B,B6)</f>
+        <v>400</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A6,B:B,B6)</f>
+        <v>800</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A7)</f>
+        <v>200</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A7)</f>
+        <v>600</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A7,B:B,B7)</f>
+        <v>500</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A7,B:B,B7)</f>
+        <v>600</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>800</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A8)</f>
+        <v>100</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A8)</f>
+        <v>700</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A8,B:B,B8)</f>
+        <v>100</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A8,B:B,B8)</f>
+        <v>100</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>350</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A9)</f>
+        <v>300</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A9)</f>
+        <v>800</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A9,B:B,B9)</f>
+        <v>400</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A9,B:B,B9)</f>
+        <v>800</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A10)</f>
+        <v>200</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A10)</f>
+        <v>600</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A10,B:B,B10)</f>
+        <v>200</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A10,B:B,B10)</f>
+        <v>350</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>3</v>
+      <c r="D11" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A11)</f>
+        <v>100</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A11)</f>
+        <v>700</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,A11,B:B,B11)</f>
+        <v>450</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,A11,B:B,B11)</f>
+        <v>700</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <f aca="false">_xlfn.MINIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <f aca="false">_xlfn.MAXIFS(C:C,A:A,"ZZZZ")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
